--- a/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 14,11</t>
+          <t>-7,81; 14,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 15,05</t>
+          <t>-6,61; 15,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -16,05</t>
+          <t>-34,12; -16,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 16,77</t>
+          <t>-5,06; 15,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 15,78</t>
+          <t>-4,77; 16,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,29; -18,97</t>
+          <t>-34,27; -19,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 11,9</t>
+          <t>-2,63; 12,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 13,34</t>
+          <t>-1,88; 13,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,88; -20,47</t>
+          <t>-31,59; -20,29</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 54,02</t>
+          <t>-21,34; 57,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 56,64</t>
+          <t>-17,87; 59,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,47; -61,58</t>
+          <t>-89,83; -61,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 58,93</t>
+          <t>-14,6; 57,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 55,69</t>
+          <t>-12,58; 57,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,59; -67,49</t>
+          <t>-93,2; -68,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 42,13</t>
+          <t>-7,19; 44,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 47,15</t>
+          <t>-5,75; 47,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,12; -71,59</t>
+          <t>-89,13; -71,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 15,18</t>
+          <t>-1,42; 15,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 15,64</t>
+          <t>-0,99; 15,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -0,66</t>
+          <t>-15,37; -0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 4,5</t>
+          <t>-11,98; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 9,69</t>
+          <t>-6,85; 10,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -16,71</t>
+          <t>-30,87; -16,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 7,45</t>
+          <t>-5,27; 7,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 9,25</t>
+          <t>-1,86; 9,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -11,21</t>
+          <t>-21,73; -11,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 78,78</t>
+          <t>-6,25; 82,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 84,78</t>
+          <t>-3,4; 84,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -2,42</t>
+          <t>-54,31; -1,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 16,38</t>
+          <t>-32,05; 19,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 34,53</t>
+          <t>-19,1; 34,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,58; -57,12</t>
+          <t>-80,44; -56,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 29,67</t>
+          <t>-16,48; 27,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 35,01</t>
+          <t>-6,03; 38,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,83; -42,94</t>
+          <t>-67,16; -43,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 16,3</t>
+          <t>-3,56; 15,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 19,07</t>
+          <t>1,25; 19,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 33,68</t>
+          <t>-11,78; 30,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 23,24</t>
+          <t>3,51; 23,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 25,2</t>
+          <t>7,1; 25,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 5,56</t>
+          <t>-11,25; 5,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 17,62</t>
+          <t>3,56; 17,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 19,93</t>
+          <t>7,01; 20,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 18,8</t>
+          <t>-7,83; 19,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 77,54</t>
+          <t>-11,98; 71,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 90,8</t>
+          <t>3,27; 90,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 192,89</t>
+          <t>-43,48; 128,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,37; 137,81</t>
+          <t>13,4; 139,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,86; 151,24</t>
+          <t>25,02; 147,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 35,67</t>
+          <t>-44,15; 31,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,0; 85,45</t>
+          <t>13,1; 86,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,75; 101,17</t>
+          <t>25,7; 99,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,21; 90,39</t>
+          <t>-32,58; 95,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 29,74</t>
+          <t>9,91; 28,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 16,28</t>
+          <t>-1,86; 16,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 8,47</t>
+          <t>-9,75; 6,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,27; 33,75</t>
+          <t>17,07; 33,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 23,02</t>
+          <t>4,95; 22,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 18,58</t>
+          <t>2,15; 18,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,13; 28,97</t>
+          <t>16,12; 28,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,19</t>
+          <t>4,47; 17,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,7</t>
+          <t>-1,74; 10,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,24; 116,32</t>
+          <t>28,02; 107,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 60,5</t>
+          <t>-5,8; 63,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 33,08</t>
+          <t>-27,29; 25,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57,13; 165,97</t>
+          <t>59,24; 165,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,11; 115,27</t>
+          <t>18,02; 110,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 89,5</t>
+          <t>7,08; 85,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,51; 119,39</t>
+          <t>52,64; 114,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,55; 69,23</t>
+          <t>14,23; 67,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 41,55</t>
+          <t>-5,84; 40,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,16</t>
+          <t>5,33; 14,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,98</t>
+          <t>2,16; 11,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,41</t>
+          <t>-12,01; 3,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,66</t>
+          <t>5,97; 15,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,0</t>
+          <t>4,84; 14,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -7,06</t>
+          <t>-14,63; -6,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,26</t>
+          <t>7,16; 13,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,5</t>
+          <t>5,08; 11,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -2,76</t>
+          <t>-12,06; -4,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,67; 59,94</t>
+          <t>17,53; 56,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,85; 46,3</t>
+          <t>6,97; 43,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 14,36</t>
+          <t>-41,05; 18,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,91; 57,26</t>
+          <t>19,69; 58,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,63; 55,17</t>
+          <t>15,97; 56,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -26,22</t>
+          <t>-48,83; -26,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,88; 49,8</t>
+          <t>24,1; 51,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,61; 43,42</t>
+          <t>17,33; 43,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -8,34</t>
+          <t>-41,32; -14,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 14,53</t>
+          <t>-8,91; 13,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 15,66</t>
+          <t>-7,41; 14,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,12; -16,97</t>
+          <t>-34,14; -17,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 15,92</t>
+          <t>-6,61; 14,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 16,32</t>
+          <t>-4,28; 17,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -19,06</t>
+          <t>-35,17; -19,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 12,23</t>
+          <t>-3,36; 12,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 13,87</t>
+          <t>-2,57; 12,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,59; -20,29</t>
+          <t>-32,42; -20,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 57,93</t>
+          <t>-23,74; 50,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 59,22</t>
+          <t>-19,78; 56,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,83; -61,87</t>
+          <t>-89,89; -61,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 57,52</t>
+          <t>-17,58; 52,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 57,9</t>
+          <t>-11,56; 61,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -68,87</t>
+          <t>-92,85; -66,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 44,3</t>
+          <t>-9,33; 42,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 47,41</t>
+          <t>-7,35; 44,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,13; -71,4</t>
+          <t>-89,23; -72,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 15,91</t>
+          <t>-1,84; 15,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 15,53</t>
+          <t>-1,82; 14,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -0,32</t>
+          <t>-15,32; -0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 5,92</t>
+          <t>-11,84; 5,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 10,08</t>
+          <t>-7,47; 10,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -16,45</t>
+          <t>-30,56; -16,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 7,31</t>
+          <t>-4,8; 7,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,6</t>
+          <t>-2,29; 9,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; -11,18</t>
+          <t>-21,44; -10,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 82,77</t>
+          <t>-8,29; 81,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 84,43</t>
+          <t>-7,58; 75,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,31; -1,4</t>
+          <t>-54,37; -2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 19,13</t>
+          <t>-32,13; 19,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 34,67</t>
+          <t>-19,78; 34,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,44; -56,32</t>
+          <t>-79,58; -55,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 27,81</t>
+          <t>-14,52; 28,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 38,01</t>
+          <t>-7,25; 38,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,16; -43,57</t>
+          <t>-67,15; -42,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 15,51</t>
+          <t>-3,15; 17,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 19,98</t>
+          <t>0,45; 19,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 30,74</t>
+          <t>-12,27; 31,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 23,13</t>
+          <t>3,87; 22,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 25,02</t>
+          <t>7,26; 25,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 5,1</t>
+          <t>-10,51; 5,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 17,3</t>
+          <t>3,51; 16,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 20,23</t>
+          <t>6,53; 19,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 19,64</t>
+          <t>-7,71; 19,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 71,62</t>
+          <t>-10,26; 82,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 90,39</t>
+          <t>2,17; 94,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,48; 128,82</t>
+          <t>-45,27; 129,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 139,65</t>
+          <t>15,57; 141,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 147,18</t>
+          <t>26,9; 149,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 31,7</t>
+          <t>-41,81; 36,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 86,66</t>
+          <t>13,41; 83,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,7; 99,61</t>
+          <t>23,59; 96,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 95,11</t>
+          <t>-31,17; 99,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 28,94</t>
+          <t>10,04; 28,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,41</t>
+          <t>-1,96; 15,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 6,91</t>
+          <t>-9,79; 7,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,07; 33,74</t>
+          <t>15,59; 33,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 22,73</t>
+          <t>6,85; 23,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 18,43</t>
+          <t>1,61; 18,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,12; 28,3</t>
+          <t>16,59; 29,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 17,15</t>
+          <t>4,99; 17,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 10,41</t>
+          <t>-0,79; 10,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,02; 107,88</t>
+          <t>26,91; 108,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 63,86</t>
+          <t>-6,07; 58,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 25,56</t>
+          <t>-27,98; 27,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59,24; 165,79</t>
+          <t>54,27; 163,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,02; 110,38</t>
+          <t>24,07; 114,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 85,67</t>
+          <t>3,78; 88,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,64; 114,3</t>
+          <t>51,75; 114,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,23; 67,15</t>
+          <t>14,74; 68,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 40,98</t>
+          <t>-2,67; 43,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,83</t>
+          <t>5,19; 15,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,33</t>
+          <t>1,97; 11,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 3,93</t>
+          <t>-12,15; 3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,08</t>
+          <t>5,91; 14,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,03</t>
+          <t>5,17; 14,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -6,85</t>
+          <t>-14,75; -6,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,57</t>
+          <t>6,82; 13,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,51</t>
+          <t>4,87; 11,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,0</t>
+          <t>-12,44; -3,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,53; 56,42</t>
+          <t>17,01; 59,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,97; 43,22</t>
+          <t>6,6; 44,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 18,05</t>
+          <t>-41,18; 14,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,69; 58,15</t>
+          <t>19,92; 57,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,97; 56,1</t>
+          <t>16,86; 55,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,83; -26,66</t>
+          <t>-49,41; -26,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,1; 51,63</t>
+          <t>23,0; 50,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,33; 43,63</t>
+          <t>16,82; 43,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -14,38</t>
+          <t>-42,03; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-26,8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-25,15</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-27,02</t>
+          <t>-25,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-26,16</t>
+          <t>-26,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 13,16</t>
+          <t>-4,31; 16,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 14,97</t>
+          <t>-4,6; 15,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,14; -17,19</t>
+          <t>-34,4; -18,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 14,45</t>
+          <t>-8,3; 14,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 17,49</t>
+          <t>-6,72; 15,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -19,9</t>
+          <t>-33,28; -16,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 12,15</t>
+          <t>-3,54; 11,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 12,7</t>
+          <t>-1,68; 13,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,42; -20,57</t>
+          <t>-31,71; -20,46</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-83,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-79,45%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-84,08%</t>
+          <t>-79,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-81,99%</t>
+          <t>-81,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 50,37</t>
+          <t>-12,77; 58,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 56,0</t>
+          <t>-12,83; 55,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,89; -61,63</t>
+          <t>-92,37; -64,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 52,86</t>
+          <t>-22,47; 54,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 61,82</t>
+          <t>-17,86; 56,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,85; -66,77</t>
+          <t>-89,4; -61,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 42,7</t>
+          <t>-10,02; 42,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 44,51</t>
+          <t>-4,83; 47,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,23; -72,34</t>
+          <t>-88,94; -71,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,79</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-23,3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,76</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-23,5</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,34</t>
+          <t>-16,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 15,84</t>
+          <t>-12,74; 4,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 14,9</t>
+          <t>-6,88; 9,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -0,45</t>
+          <t>-30,15; -16,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 5,52</t>
+          <t>-2,08; 15,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 10,04</t>
+          <t>-0,86; 15,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,56; -16,37</t>
+          <t>-14,79; -0,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,28</t>
+          <t>-4,94; 7,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,98</t>
+          <t>-2,21; 9,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,44; -10,65</t>
+          <t>-21,23; -10,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-11,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-69,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>29,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>29,9%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-32,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-11,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-69,93%</t>
+          <t>-31,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-56,56%</t>
+          <t>-55,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 81,43</t>
+          <t>-33,09; 16,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 75,85</t>
+          <t>-17,82; 34,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,37; -2,13</t>
+          <t>-79,23; -55,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 19,8</t>
+          <t>-7,54; 78,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 34,73</t>
+          <t>-5,23; 84,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,58; -55,28</t>
+          <t>-53,25; -0,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 28,45</t>
+          <t>-15,9; 29,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 38,93</t>
+          <t>-6,58; 35,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -42,77</t>
+          <t>-66,24; -41,84</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,19</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,64</t>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-4,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 17,11</t>
+          <t>4,57; 23,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 19,47</t>
+          <t>6,43; 25,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 31,88</t>
+          <t>-10,61; 5,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 22,88</t>
+          <t>-2,19; 16,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 25,35</t>
+          <t>1,34; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 5,59</t>
+          <t>-15,27; 1,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 16,7</t>
+          <t>3,61; 17,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 19,17</t>
+          <t>6,84; 19,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 19,82</t>
+          <t>-10,54; 1,67</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-12,67%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>27,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>39,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65,54%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,34%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,6%</t>
+          <t>-26,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>-20,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 82,48</t>
+          <t>16,37; 137,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 94,0</t>
+          <t>22,86; 151,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 129,38</t>
+          <t>-42,25; 35,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 141,83</t>
+          <t>-7,5; 77,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,9; 149,31</t>
+          <t>3,57; 90,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 36,42</t>
+          <t>-50,3; 7,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 83,71</t>
+          <t>14,0; 85,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,59; 96,19</t>
+          <t>25,75; 101,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 99,3</t>
+          <t>-39,53; 10,0</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25,28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15,07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10,69</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>20,09</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25,28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,07</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 28,9</t>
+          <t>16,27; 33,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 15,85</t>
+          <t>5,95; 23,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 7,35</t>
+          <t>2,49; 18,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 33,2</t>
+          <t>9,93; 29,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,36</t>
+          <t>-1,57; 16,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 18,69</t>
+          <t>-9,26; 7,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 29,23</t>
+          <t>16,13; 28,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 17,35</t>
+          <t>4,39; 17,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 10,79</t>
+          <t>-1,44; 10,08</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>102,33%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>64,88%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,61%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-3,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>102,33%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>-5,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,91; 108,05</t>
+          <t>57,13; 165,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 58,78</t>
+          <t>21,11; 115,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 27,62</t>
+          <t>9,41; 91,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54,27; 163,41</t>
+          <t>28,24; 116,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,07; 114,51</t>
+          <t>-4,54; 60,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 88,84</t>
+          <t>-27,16; 30,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,75; 114,46</t>
+          <t>52,51; 119,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,74; 68,79</t>
+          <t>14,55; 69,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 43,24</t>
+          <t>-4,74; 40,16</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-10,57</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>9,93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>6,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,88</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-9,72</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,99</t>
+          <t>-10,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,21</t>
+          <t>5,53; 14,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,23</t>
+          <t>4,85; 14,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 3,72</t>
+          <t>-14,77; -6,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,63</t>
+          <t>4,77; 15,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,24</t>
+          <t>2,59; 11,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -6,74</t>
+          <t>-14,13; -5,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,54</t>
+          <t>6,89; 13,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,43</t>
+          <t>5,0; 11,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -3,56</t>
+          <t>-13,04; -7,14</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-37,83%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,75%</t>
+          <t>-34,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-32,08%</t>
+          <t>-36,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,01; 59,31</t>
+          <t>17,91; 57,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,6; 44,69</t>
+          <t>15,63; 55,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 14,99</t>
+          <t>-48,51; -25,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,92; 57,51</t>
+          <t>15,67; 59,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,86; 55,33</t>
+          <t>7,85; 46,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -26,73</t>
+          <t>-45,9; -20,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,0; 50,72</t>
+          <t>22,88; 49,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,82; 43,64</t>
+          <t>16,61; 43,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -12,02</t>
+          <t>-44,25; -27,12</t>
         </is>
       </c>
     </row>
